--- a/app/views/plans/excels/zgis-places.xlsx
+++ b/app/views/plans/excels/zgis-places.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093D68C1-4F5C-4142-80B2-5AF566C2141E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AD17E5-D6D9-44C0-BE47-473436F40DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45740" yWindow="3620" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作付計画" sheetId="3" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>__xl$gis__</t>
   </si>
@@ -109,6 +109,16 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>耕地番号</t>
+    <rPh sb="0" eb="2">
+      <t>コウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -116,7 +126,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="180" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.0_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -239,7 +249,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -543,53 +553,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="17.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.6328125" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8.1796875" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="16" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="2"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="10"/>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -618,115 +633,115 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A2,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A2,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B3" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A3,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A3,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A4,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A4,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A5,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A5,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A6,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A6,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A7,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A7,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A8,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A8,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A9,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A9,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A10,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A10,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A11,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A11,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A12,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A12,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A13,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A13,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A14,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A14,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A15,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A15,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A16,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A16,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A17,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A17,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A18,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A18,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B19" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A19,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A19,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B20" s="16">
-        <f>SUMIF(作付計画!E:E,作付集計!A20,作付計画!D:D)</f>
+        <f>SUMIF(作付計画!F:F,作付集計!A20,作付計画!E:E)</f>
         <v>0</v>
       </c>
     </row>
@@ -746,6 +761,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FD1DD97C84CAA34CB91F63533262373F" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="07d89e7ee254bb3efae657754263557c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8b57cd28-001b-4929-a28f-607d10555978" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e85f1ab1302870a4ae3f9372b6b7e2a0" ns2:_="">
     <xsd:import namespace="8b57cd28-001b-4929-a28f-607d10555978"/>
@@ -903,22 +933,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCE65FF8-DADA-4191-A681-F54511CB9804}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B4265D3-6398-4957-A411-465DE6535C7B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BD78979-59C9-4349-B345-87D10294C24A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -934,21 +966,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B4265D3-6398-4957-A411-465DE6535C7B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCE65FF8-DADA-4191-A681-F54511CB9804}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>